--- a/data/credit_bond_2026-08-19.xlsx
+++ b/data/credit_bond_2026-08-19.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-19" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-20" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-19</t>
+          <t>数据来源：DM    2026-08-20</t>
         </is>
       </c>
     </row>
@@ -682,17 +682,17 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26恒丰银行债01</t>
+          <t>26国耀融汇MTN004</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>08-18 17:00</t>
+          <t>08-19 18:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>212680022.IB</t>
+          <t>102683198.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -701,60 +701,56 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>80.0</v>
+        <v>4.0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>80.0</v>
+        <v>4.0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>34.07</v>
-      </c>
+          <t>1.70 ~ 1.98</t>
+        </is>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25恒丰银行债02</t>
+          <t>24国药租赁MTN005</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>1.76Y</t>
+          <t>2.99Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.5795</t>
+          <t>1.9565</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.5950/--</t>
+          <t>1.9500/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司</t>
+          <t>国耀融汇融资租赁有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>08-18 09:00</t>
+          <t>08-19 09:00</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -771,12 +767,12 @@
       <c r="U3" s="3"/>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.91%~2.01%</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
@@ -784,31 +780,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Y3" s="3"/>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将用于优化发行人负债结构，充实营运资金，促进业务稳健发展。</t>
+          <t>本期中期票据募集资金4亿元,所募集资金拟用于归还发行人本部即将到期的债务融资工具[24国药租赁MTN007]</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰证券股份有限公司,中国银行股份有限公司,中国邮政储蓄银行股份有限公司,上海浦东发展银行股份有限公司,渤海银行股份有限公司</t>
+          <t>平安银行股份有限公司,上海银行股份有限公司</t>
         </is>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>恒丰银行股份有限公司2026年第一期金融债券</t>
+          <t>国耀融汇融资租赁有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
@@ -834,75 +834,961 @@
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AY3" s="4" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4" customHeight="true" ht="18.0">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>26涪陵国资MTN002A</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>08-19 18:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>102602205.IB</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>24涪陵国资MTN004B</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>4.79Y</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>1.9792</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>1.9900/1.7700</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>08-19 09:00</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>商业银行</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>股份制银行</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>银行</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
+      <c r="T4" s="3"/>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>2.00%~2.10%</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>重庆市-涪陵区</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>发行人本次债务融资工具注册金额为人民币23.30亿元,本期债券基础发行规模为0亿元,发行金额上限为7.30亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN002]</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,华泰证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第二期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2031-08-20</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>食品加工</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AU4" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
+      <c r="AV4" s="3" t="inlineStr">
         <is>
           <t>不含权</t>
         </is>
       </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AY4" s="3"/>
+    </row>
+    <row r="5" customHeight="true" ht="18.0">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>26达州投资PPN001</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>08-19 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>26达州01</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>4.70Y</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2.0756</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>--/2.0700</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>达州市投资有限公司</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>08-19 14:00</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>2.07%~2.17%</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>四川省-达州市</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>发行人本次定向债务融资工具基础发行规模0.00亿元,发行规模上限为10.00亿元,全部用于偿还到期的债务融资工具本金[23达州投资PPN001]</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>中泰证券股份有限公司,成都农村商业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>达州市投资有限公司2026年度第一期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2031-08-20</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3"/>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="AY3" s="3"/>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AY5" s="4" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6" customHeight="true" ht="18.0">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>26涪陵国资MTN002B</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>08-19 18:00</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>102602206.IB</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>25涪陵国资MTN004B</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>5.65Y</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2.1210</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>2.2000/--</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>重庆市涪陵国有资产投资经营集团有限公司</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>08-19 09:00</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>2.35%~2.45%</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>重庆市-涪陵区</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>发行人本次债务融资工具注册金额为人民币23.30亿元,本期债券基础发行规模为0亿元,发行金额上限为7.30亿元。募集资金全部用于偿还公司存量债务融资工具[23涪陵国资PPN002]</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,华泰证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>重庆市涪陵国有资产投资经营集团有限公司2026年度第二期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>2033-08-20</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>食品加工</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AY6" s="3"/>
+    </row>
+    <row r="7" customHeight="true" ht="18.0">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>26武汉开投PPN004</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>08-19 18:00</t>
+        </is>
+      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>26武汉开投PPN003</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>2.90Y</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2.0111</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>--/1.9500</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>武汉开发投资有限公司</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>08-19 15:00</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>2.08%~2.18%</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>湖北省-武汉市</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>本期定向债务融资工具发行金额5亿元,拟2.1亿元用于融资租赁业务投放,2.9亿元用于偿还公司有息负债。</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,长江证券股份有限公司,申万宏源证券有限公司,中国光大银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>武汉金融控股(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>武汉开发投资有限公司2026年度第四期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>2029-08-20</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AY7" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-08-19.xlsx
+++ b/data/credit_bond_2026-08-19.xlsx
@@ -711,8 +711,12 @@
           <t>1.70 ~ 1.98</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>69.45</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.96</t>
@@ -763,8 +767,12 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
+      <c r="T3" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>1.05</v>
+      </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -938,8 +946,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>56.01</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.98</t>
@@ -990,8 +1002,12 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
+      <c r="T4" s="4" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>1.47</v>
+      </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -1153,8 +1169,12 @@
           <t>1.80 ~ 2.60</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>72.01</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>2.13</t>
@@ -1205,8 +1225,12 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
+      <c r="T5" s="4" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -1376,8 +1400,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>71.85</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>2.23</t>
@@ -1428,8 +1456,12 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
+      <c r="T6" s="4" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>1.8</v>
+      </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -1595,8 +1627,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>70.45</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.99</t>
@@ -1647,8 +1683,12 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
+      <c r="T7" s="4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
           <t>6+</t>

--- a/data/credit_bond_2026-08-19.xlsx
+++ b/data/credit_bond_2026-08-19.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-21" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-24" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -37,6 +37,10 @@
       <sz val="12.0"/>
       <color indexed="8"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="12.0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -90,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
@@ -99,6 +103,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -149,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ1"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -163,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-21</t>
+          <t>数据来源：DM    2026-08-24</t>
         </is>
       </c>
     </row>
@@ -678,6 +688,230 @@
           <t>团费(%)</t>
         </is>
       </c>
+    </row>
+    <row r="3" customHeight="true" ht="18.0">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>26齐商银行永续债01</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>08-24 18:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>5+N</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>24齐商银行永续债01</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>2.82Y+N</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>2.5344</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>齐商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>B- 38.50</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>08-24 09:00</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>2.79%~2.89%</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>山东省-淄博市</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金在扣除发行费用后,将依据适用法律和主管部门的批准用于补充发行人其他一级资本。</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>其他金融债</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>齐商银行股份有限公司2026年无固定期限资本债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>2031-08-26</t>
+        </is>
+      </c>
+      <c r="AK3" s="3"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>城商行</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>其他一级资本工具</t>
+        </is>
+      </c>
+      <c r="AY3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AZ3" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-08-19.xlsx
+++ b/data/credit_bond_2026-08-19.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-24" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-25" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-24</t>
+          <t>数据来源：DM    2026-08-25</t>
         </is>
       </c>
     </row>
@@ -912,6 +912,446 @@
         </is>
       </c>
       <c r="AZ3" s="3"/>
+    </row>
+    <row r="4" customHeight="true" ht="18.0">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>26三峡银行三农债</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>25三峡银行绿色债01</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>2.24Y</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>1.6147</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>B- 38.68</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>08-25 09:00</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金将全部专项用于发放涉农贷款,支持乡村振兴业务发展</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,西南证券股份有限公司,重庆银行股份有限公司,恒丰银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>重庆三峡银行股份有限公司2026年"三农"专项金融债券</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AK4" s="3"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>城商行</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AZ4" s="3"/>
+    </row>
+    <row r="5" customHeight="true" ht="18.0">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>26华发集团SCP007</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>08-25 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0.74Y</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2.15 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>22华发集团MTN008</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>287D</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2.3517</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>珠海华发集团有限公司</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>C+ 32.02</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>08-25 09:00</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>广东省-珠海市</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>本期超短期融资券发行规模为15亿元,用于偿还发行人本部债务融资工具本金。[21华发集团MTN009,23华发集团MTN005]</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>北京银行股份有限公司,上海银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>超短期融资券(SCP)</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>珠海华发集团有限公司2026年度第七期超短期融资券</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr">
+        <is>
+          <t>2027-05-22</t>
+        </is>
+      </c>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AZ5" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-08-19.xlsx
+++ b/data/credit_bond_2026-08-19.xlsx
@@ -715,8 +715,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>36.49</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>--</t>

--- a/data/credit_bond_2026-08-19.xlsx
+++ b/data/credit_bond_2026-08-19.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -700,7 +700,11 @@
           <t>08-24 18:00</t>
         </is>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>242680030.IB</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>5+N</t>
@@ -709,17 +713,19 @@
       <c r="E3" s="4" t="n">
         <v>20.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1.75</v>
+        <v>2.65</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>36.49</v>
+        <v>126.49</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -967,7 +973,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6000</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1148,7 +1154,11 @@
           <t>08-25 18:00</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>012682145.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -1227,7 +1237,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X5" s="3"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>2.41%~2.45%</t>
+        </is>
+      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1355,7 +1369,233 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AZ5" s="3"/>
+      <c r="AZ5" s="4" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6" customHeight="true" ht="18.0">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>26北部湾银行02</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>08-25 16:00</t>
+        </is>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>26北部湾银行01</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>2.98Y</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>1.6468</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>1.6500/1.6475</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>广西北部湾银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>B- 38.54</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>08-25 09:00</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>广西壮族自治区-南宁市</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金将严格遵循法律法规及监管批复要求，专项用于补充本行投放向海经济领域信贷业务所需的资金，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,光大证券股份有限公司,国海证券股份有限公司,中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>广西北部湾银行股份有限公司2026年金融债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr">
+        <is>
+          <t>2029-08-27</t>
+        </is>
+      </c>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>城商行</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AZ6" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_2026-08-19.xlsx
+++ b/data/credit_bond_2026-08-19.xlsx
@@ -1423,7 +1423,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1.6500/1.6475</t>
+          <t>1.6500/1.6499</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">

--- a/data/credit_bond_2026-08-19.xlsx
+++ b/data/credit_bond_2026-08-19.xlsx
@@ -1423,7 +1423,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1.6500/1.6499</t>
+          <t>1.6500/1.6500</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
